--- a/var/data/original_files/July 2 Articles A .xlsx
+++ b/var/data/original_files/July 2 Articles A .xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,11 +488,6 @@
           <t>Full Link</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Coordinates</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,11 +539,6 @@
           <t>https://www.world-nuclear-news.org/articles/zaporizhzhia-security-restart-and-us-fuel-discussed-in-iaea-russian-talks</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>(54.710128, 20.5105838)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,11 +590,6 @@
           <t>https://www.nucnet.org/news/wano-concludes-global-nuclear-communications-forum-in-london-6-1-2025</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>(51.4893335, -0.1440551)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -656,11 +641,6 @@
           <t>https://www.who.int/news/item/09-06-2025-fourth-meeting-of-the-international-health-regulations-(2005)-emergency-committee-regarding-the-upsurge-of-mpox-2024-temporary-recommendations</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -712,11 +692,6 @@
           <t>https://koreajoongangdaily.joins.com/news/2025-06-10/national/northKorea/North-Korea-constructing-new-nuclear-facility-IAEA-reports/2326730</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>(39.8022323, 125.7520365)</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -768,11 +743,6 @@
           <t>https://ifpnews.com/snsc-israeli-secret-nuclear-sites-iranian-facilities/</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -824,11 +794,6 @@
           <t>https://ifpnews.com/iaea-chief-israeli-attack-iran-nuclear-weapons/</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -880,11 +845,6 @@
           <t>https://www.kurdistan24.net/en/story/844844/iran-us-to-hold-new-round-of-nuclear-talks-in-muscat-on-sunday</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>(23.6123628, 58.5938134)</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -936,11 +896,6 @@
           <t>https://www.the-express.com/news/world-news/174310/russia-deploys-nuclear-bomber-alaska</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>(55.625578, 37.6063916)</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -992,11 +947,6 @@
           <t>https://globalbiodefense.com/2025/06/09/high-stakes-in-sichuan-a-decade-of-deadly-h5n6-infections-raises-urgency-for-avian-influenza-control/</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>(30.5000001, 102.4999999)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1048,11 +998,6 @@
           <t>https://apnews.com/article/iran-israel-nuclear-programs-iaea-94c0f87c357fd72169dee198cb6800a7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1104,11 +1049,6 @@
           <t>https://www.msn.com/en-ie/news/world/bombs-explode-at-u-s-base-in-japan-here-s-what-we-know/ar-AA1GpBWj</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>(26.5707754, 128.0255901)</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1160,11 +1100,6 @@
           <t>https://news.az/news/australian-scientists-uncover-rapid-evolution-patterns-of-covid-19-virus</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>(-33.8698439, 151.2082848)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1216,11 +1151,6 @@
           <t>https://www.countryman.com.au/countryman/news/emergency-animal-disease-outbreak-management-put-to-test-in-joint-state-and-federal-government-exercise-c-18930997</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>(-28.77035, 114.6147159)</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1272,11 +1202,6 @@
           <t>https://www.iaea.org/newscenter/news/director-general-briefs-board-on-iran-developments-syria-ukraine-and-more</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1328,11 +1253,6 @@
           <t>https://www.reuters.com/world/europe/russia-says-it-is-ready-remove-excess-nuclear-materials-iran-2025-06-11/</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>(55.625578, 37.6063916)</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1384,11 +1304,6 @@
           <t>https://en.mehrnews.com/news/232941/Iran-to-triple-its-nuclear-power-plants-capacity</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1440,11 +1355,6 @@
           <t>https://edition.cnn.com/2025/06/12/politics/trump-israel-iran-strike</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1483,7 +1393,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,11 +1404,6 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>https://asharq.com/politics/139135/%D9%85%D8%AC%D9%84%D8%B3-%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86-%D8%A7%D9%84%D8%AE%D9%84%D9%8A%D8%AC%D9%8A-%D9%84%D9%85-%D9%86%D8%B1%D8%B5%D8%AF-%D9%85%D8%B3%D8%AA%D9%88%D9%8A%D8%A7%D8%AA-%D8%A5%D8%B4%D8%B9%D8%A7%D8%B9%D9%8A%D8%A9-%D8%BA%D9%8A%D8%B1-%D8%B7%D8%A8%D9%8A%D8%B9%D9%8A%D8%A9/</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>(23.333333, 45.333333)</t>
         </is>
       </c>
     </row>
@@ -1552,11 +1457,6 @@
           <t>https://www.reuters.com/world/middle-east/iran-says-nuclear-talks-with-us-meaningless-after-israel-attack-2025-06-14/</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1608,11 +1508,6 @@
           <t>https://www.understandingwar.org/backgrounder/iran-update-special-edition-israeli-strikes-iran-june-13-2025-200-pm-et</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1651,7 +1546,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human, Infrastructure</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1664,46 +1559,45 @@
           <t>https://nypost.com/2025/06/13/world-news/idf-headquarters-hit-by-iranian-missile-attack-as-islamic-republic-launches-barrage-of-missiles-at-tel-aviv/?utm_source=chatgpt.com</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>‘Significant damage’ after IDF headquarters hit by Iranian missile attack as Islamic Republic launches barrage of missiles at Tel Aviv</t>
+          <t>«هيئة الرقابة النووية»: بيئة السعودية آمنة من أي عواقب إشعاعية</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Isreal</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1713,10 +1607,9 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://nypost.com/2025/06/13/world-news/idf-headquarters-hit-by-iranian-missile-attack-as-islamic-republic-launches-barrage-of-missiles-at-tel-aviv/?utm_source=chatgpt.com</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>https://www.alriyadh.com/2136622</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1726,26 +1619,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>«هيئة الرقابة النووية»: بيئة السعودية آمنة من أي عواقب إشعاعية</t>
+          <t>Israeli official says 'it was a mistake' to say Bushehr was hit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Isreal</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45821</v>
+        <v>45827</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1755,7 +1648,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1765,12 +1658,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.alriyadh.com/2136622</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>(23.333333, 45.333333)</t>
+          <t>https://www.reuters.com/world/middle-east/israeli-military-says-it-struck-nuclear-sites-including-bushehr-gulf-coast-2025-06-19/</t>
         </is>
       </c>
     </row>
@@ -1787,17 +1675,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israeli official says 'it was a mistake' to say Bushehr was hit</t>
+          <t>Russia warns strike on Iran's Bushehr nuclear plant could cause 'Chernobyl-style catastrophe'</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Isreal</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -1816,15 +1704,14 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/middle-east/israeli-military-says-it-struck-nuclear-sites-including-bushehr-gulf-coast-2025-06-19/</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>https://www.yahoo.com/news/russia-warns-strike-irans-bushehr-115609346.html?guce_referrer=aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;guce_referrer_sig=AQAAAM68hbx0j9wVe69GUZM_zvwNwKc7ox9ObagQdFLMjT37_-OEFf-4hvUaSguJTC0kTn0tP4sr2-h9nfZA8W2pmfNFAQRR-BDqa4toVRYO_rOh9ZQBQiwq1L1nH52-af8BQTo8AyWZ8zdxfJFtQtWMbxXK7cqqp0wTPrw8yGJOlmP1&amp;guccounter=2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1839,21 +1726,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia warns strike on Iran's Bushehr nuclear plant could cause 'Chernobyl-style catastrophe'</t>
+          <t>إيران تؤكد إخلاء منشآتها النووية قبل الهجوم الأمريكي</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Fordow</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45827</v>
+        <v>45830</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1873,19 +1760,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.yahoo.com/news/russia-warns-strike-irans-bushehr-115609346.html?guce_referrer=aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;guce_referrer_sig=AQAAAM68hbx0j9wVe69GUZM_zvwNwKc7ox9ObagQdFLMjT37_-OEFf-4hvUaSguJTC0kTn0tP4sr2-h9nfZA8W2pmfNFAQRR-BDqa4toVRYO_rOh9ZQBQiwq1L1nH52-af8BQTo8AyWZ8zdxfJFtQtWMbxXK7cqqp0wTPrw8yGJOlmP1&amp;guccounter=2</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>(55.625578, 37.6063916)</t>
+          <t>https://www.eremnews.com/news/world/bugin06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1895,7 +1777,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>إيران تؤكد إخلاء منشآتها النووية قبل الهجوم الأمريكي</t>
+          <t>U.S. B-2 bombers were involved in strikes on Iran's nuclear sites</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1924,34 +1806,29 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.eremnews.com/news/world/bugin06</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>(34.9460464, 50.7409863)</t>
+          <t>https://www.reuters.com/business/aerospace-defense/us-b-2-bombers-involved-iran-strikes-us-official-says-2025-06-22/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>U.S. B-2 bombers were involved in strikes on Iran's nuclear sites</t>
+          <t>أعلنت هيئة الطاقة الذرية الإيرانية، صباح الأحد، أنه لا يوجد أي خطر إشعاعي يهدد السكان بعد تعرض 3 مواقع نووية في البلاد لقصف أميركي</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1961,7 +1838,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fordow</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -1980,17 +1857,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/aerospace-defense/us-b-2-bombers-involved-iran-strikes-us-official-says-2025-06-22/</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>(34.9460464, 50.7409863)</t>
+          <t>https://www.skynewsarabia.com/middle-east/1804518-%D8%A7%D9%95%D9%8A%D8%B1%D8%A7%D9%86-%D8%A8%D9%8A%D8%A7%D9%86%D8%A7%D9%86-%D8%A8%D8%B4%D8%A7%D9%94%D9%86-%D8%A7%D9%84%D8%AA%D8%B3%D8%B1%D8%A8-%D8%A7%D9%84%D8%A7%D9%95%D8%B4%D8%B9%D8%A7%D8%B9%D9%8A-%D8%A7%D9%84%D8%B6%D8%B1%D8%A8%D8%A7%D8%AA-%D8%A7%D9%84%D8%A7%D9%94%D9%85%D9%8A%D8%B1%D9%83%D9%8A%D8%A9</t>
         </is>
       </c>
     </row>
@@ -2002,26 +1874,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>أعلنت هيئة الطاقة الذرية الإيرانية، صباح الأحد، أنه لا يوجد أي خطر إشعاعي يهدد السكان بعد تعرض 3 مواقع نووية في البلاد لقصف أميركي</t>
+          <t>UN Security Council meets on Iran as Russia, China push for a ceasefire</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45830</v>
+        <v>45831</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2036,24 +1908,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.skynewsarabia.com/middle-east/1804518-%D8%A7%D9%95%D9%8A%D8%B1%D8%A7%D9%86-%D8%A8%D9%8A%D8%A7%D9%86%D8%A7%D9%86-%D8%A8%D8%B4%D8%A7%D9%94%D9%86-%D8%A7%D9%84%D8%AA%D8%B3%D8%B1%D8%A8-%D8%A7%D9%84%D8%A7%D9%95%D8%B4%D8%B9%D8%A7%D8%B9%D9%8A-%D8%A7%D9%84%D8%B6%D8%B1%D8%A8%D8%A7%D8%AA-%D8%A7%D9%84%D8%A7%D9%94%D9%85%D9%8A%D8%B1%D9%83%D9%8A%D8%A9</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
+          <t>https://www.reuters.com/world/middle-east/un-security-council-meet-sunday-over-us-strikes-iran-2025-06-22/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2063,31 +1930,31 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UN Security Council meets on Iran as Russia, China push for a ceasefire</t>
+          <t>Israel says struck ‘dozens’ of sites in Iran on Sunday</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45831</v>
+        <v>45830</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Infrastructure</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2097,39 +1964,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/middle-east/un-security-council-meet-sunday-over-us-strikes-iran-2025-06-22/</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>(40.7127281, -74.0060152)</t>
+          <t>https://english.alarabiya.net/News/middle-east/2025/06/22/iran-media-reports-massive-blast-in-bushehr-province-home-to-nuclear-reactor</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel says struck ‘dozens’ of sites in Iran on Sunday</t>
+          <t>مجلس التعاون الخليجي: لا مؤشرات على تسرب إشعاعي في المنطقة</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2139,33 +2001,28 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/middle-east/2025/06/22/iran-media-reports-massive-blast-in-bushehr-province-home-to-nuclear-reactor</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
+          <t>https://www.rowadalaamal.com/%D9%85%D8%AC%D9%84%D8%B3-%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86-%D9%8A%D8%A4%D9%83%D8%AF-%D9%84%D8%A7-%D9%85%D8%B3%D8%AA%D9%88%D9%8A%D8%A7%D8%AA-%D8%A5%D8%B4%D8%B9%D8%A7%D8%B9%D9%8A%D8%A9-%D8%BA/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2175,7 +2032,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel says struck ‘dozens’ of sites in Iran on Sunday</t>
+          <t>برلمان إيران يبحث تعليق التعاون مع الوكالة الدولية للطاقة الذرية</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2189,13 +2046,13 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45830</v>
+        <v>45831</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2204,17 +2061,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/middle-east/2025/06/22/iran-media-reports-massive-blast-in-bushehr-province-home-to-nuclear-reactor</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
+          <t>https://www.alarabiya.net/amp/iran/2025/06/23/%D8%A8%D8%B1%D9%84%D9%85%D8%A7%D9%86-%D8%A7%D9%8A%D8%B1%D8%A7%D9%86-%D9%8A%D8%A8%D8%AD%D8%AB-%D8%AA%D8%B9%D9%84%D9%8A%D9%82-%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86-%D9%85%D8%B9-%D8%A7%D9%84%D9%88%D9%83%D8%A7%D9%84%D8%A9-%D8%A7%D9%84%D8%AF%D9%88%D9%84%D9%8A%D8%A9-%D9%84%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D8%A7%D9%84%D8%B0%D8%B1%D9%8A%D8%A9</t>
         </is>
       </c>
     </row>
@@ -2226,26 +2078,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>مجلس التعاون الخليجي: لا مؤشرات على تسرب إشعاعي في المنطقة</t>
+          <t>إيران تقر قانونا لتعليق التعاون مع وكالة الطاقة الذرية</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45830</v>
+        <v>45833</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2255,22 +2107,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.rowadalaamal.com/%D9%85%D8%AC%D9%84%D8%B3-%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86-%D9%8A%D8%A4%D9%83%D8%AF-%D9%84%D8%A7-%D9%85%D8%B3%D8%AA%D9%88%D9%8A%D8%A7%D8%AA-%D8%A5%D8%B4%D8%B9%D8%A7%D8%B9%D9%8A%D8%A9-%D8%BA/</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>(23.333333, 45.333333)</t>
+          <t>https://www.alghad.tv/%D8%A3%D8%AE%D8%A8%D8%A7%D8%B1-%D8%A7%D9%84%D8%BA%D8%AF/news/%D8%A5%D9%8A%D8%B1%D8%A7%D9%86-%D8%AA%D9%82%D8%B1-%D9%82%D8%A7%D9%86%D9%88%D9%86%D8%A7-%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%82-%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86-%D9%85%D8%B9-%D9%88%D9%83%D8%A7%D9%84%D8%A9-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D8%A7%D9%84%D8%B0%D8%B1%D9%8A%D8%A9</t>
         </is>
       </c>
     </row>
@@ -2287,21 +2134,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>برلمان إيران يبحث تعليق التعاون مع الوكالة الدولية للطاقة الذرية</t>
+          <t>U.S. initial damage report: Iran nuclear program set back by months, not obliterated</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45831</v>
+        <v>45833</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2316,17 +2163,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.alarabiya.net/amp/iran/2025/06/23/%D8%A8%D8%B1%D9%84%D9%85%D8%A7%D9%86-%D8%A7%D9%8A%D8%B1%D8%A7%D9%86-%D9%8A%D8%A8%D8%AD%D8%AB-%D8%AA%D8%B9%D9%84%D9%8A%D9%82-%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86-%D9%85%D8%B9-%D8%A7%D9%84%D9%88%D9%83%D8%A7%D9%84%D8%A9-%D8%A7%D9%84%D8%AF%D9%88%D9%84%D9%8A%D8%A9-%D9%84%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D8%A7%D9%84%D8%B0%D8%B1%D9%8A%D8%A9</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
+          <t>https://www.washingtonpost.com/national-security/2025/06/24/us-iran-bomb-assessment-nuclear-sites-not-destroyed/</t>
         </is>
       </c>
     </row>
@@ -2338,26 +2180,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical, Biological, Radiological, Nuclear, Explosive</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>إيران تقر قانونا لتعليق التعاون مع وكالة الطاقة الذرية</t>
+          <t>مركز أبوظبي لإدارة المواد الخطرة يطلق منصة «أدهم» لتعزيز التداول الآمن للمواد الخطِرة</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45833</v>
+        <v>45835</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2367,109 +2209,99 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.alghad.tv/%D8%A3%D8%AE%D8%A8%D8%A7%D8%B1-%D8%A7%D9%84%D8%BA%D8%AF/news/%D8%A5%D9%8A%D8%B1%D8%A7%D9%86-%D8%AA%D9%82%D8%B1-%D9%82%D8%A7%D9%86%D9%88%D9%86%D8%A7-%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%82-%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86-%D9%85%D8%B9-%D9%88%D9%83%D8%A7%D9%84%D8%A9-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D8%A7%D9%84%D8%B0%D8%B1%D9%8A%D8%A9</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
+          <t>https://www.mediaoffice.abudhabi/ar/environment/abu-dhabi-hazardous-materials-management-centre-launches-adhm-platform-to-enhance-safe-handling-of-hazardous-materials/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>U.S. initial damage report: Iran nuclear program set back by months, not obliterated</t>
+          <t>Mass Needle Attacks at French Festival Leave Nearly 150 Pricked</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.washingtonpost.com/national-security/2025/06/24/us-iran-bomb-assessment-nuclear-sites-not-destroyed/</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
+          <t>https://travelnoire.com/needle-attacks</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear, Radiological</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>مركز أبوظبي لإدارة المواد الخطرة يطلق منصة «أدهم» لتعزيز التداول الآمن للمواد الخطِرة</t>
+          <t>Safety of Nuclear Fuel Reprocessing Facilities</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45835</v>
+        <v>45840</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2479,7 +2311,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2489,12 +2321,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.mediaoffice.abudhabi/ar/environment/abu-dhabi-hazardous-materials-management-centre-launches-adhm-platform-to-enhance-safe-handling-of-hazardous-materials/</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>(24.4538352, 54.3774014)</t>
+          <t>https://www.iaea.org/publications/15774/safety-of-nuclear-fuel-reprocessing-facilities</t>
         </is>
       </c>
     </row>
@@ -2506,26 +2333,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>مركز أبوظبي لإدارة المواد الخطرة يطلق منصة «أدهم» لتعزيز التداول الآمن للمواد الخطِرة</t>
+          <t>World’s first nuclear microreactor test bed launches at Idaho National Laboratory</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45835</v>
+        <v>45840</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2545,12 +2372,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.mediaoffice.abudhabi/ar/environment/abu-dhabi-hazardous-materials-management-centre-launches-adhm-platform-to-enhance-safe-handling-of-hazardous-materials/</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>(24.4538352, 54.3774014)</t>
+          <t>https://interestingengineering.com/energy/dome-microreactor-testing-westinghouse-radiant</t>
         </is>
       </c>
     </row>
@@ -2562,26 +2384,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>مركز أبوظبي لإدارة المواد الخطرة يطلق منصة «أدهم» لتعزيز التداول الآمن للمواد الخطِرة</t>
+          <t>World’s first nuclear reactor producing 200 tons of hydrogen daily launched in US</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45835</v>
+        <v>45840</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2601,12 +2423,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.mediaoffice.abudhabi/ar/environment/abu-dhabi-hazardous-materials-management-centre-launches-adhm-platform-to-enhance-safe-handling-of-hazardous-materials/</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>(24.4538352, 54.3774014)</t>
+          <t>https://interestingengineering.com/energy/worlds-first-nuclear-reactor-producing-hydrogen</t>
         </is>
       </c>
     </row>
@@ -2618,26 +2435,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>مركز أبوظبي لإدارة المواد الخطرة يطلق منصة «أدهم» لتعزيز التداول الآمن للمواد الخطِرة</t>
+          <t>USAID defunding could lead to 14 million deaths worldwide from infectious diseases by 2030</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45835</v>
+        <v>45839</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2647,22 +2464,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.mediaoffice.abudhabi/ar/environment/abu-dhabi-hazardous-materials-management-centre-launches-adhm-platform-to-enhance-safe-handling-of-hazardous-materials/</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>(24.4538352, 54.3774014)</t>
+          <t>https://www.cidrap.umn.edu/hivaids/usaid-defunding-could-lead-14-million-deaths-worldwide-infectious-diseases-2030</t>
         </is>
       </c>
     </row>
@@ -2674,26 +2486,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>مركز أبوظبي لإدارة المواد الخطرة يطلق منصة «أدهم» لتعزيز التداول الآمن للمواد الخطِرة</t>
+          <t>Iran’s president orders country to suspend cooperation with IAEA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45835</v>
+        <v>45840</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2703,63 +2515,58 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.mediaoffice.abudhabi/ar/environment/abu-dhabi-hazardous-materials-management-centre-launches-adhm-platform-to-enhance-safe-handling-of-hazardous-materials/</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>(24.4538352, 54.3774014)</t>
+          <t>https://gulfnews.com/world/mena/3rd-ld-writethru-250-1.500184244</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mass Needle Attacks at French Festival Leave Nearly 150 Pricked</t>
+          <t>China says it is willing to take lead in signing Southeast Asia nuclear weapon-free zone treaty</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45834</v>
+        <v>45841</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2769,19 +2576,14 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://travelnoire.com/needle-attacks</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>(48.8534951, 2.3483915)</t>
+          <t>https://www.reuters.com/world/china/china-says-it-is-willing-take-lead-signing-southeast-asia-nuclear-weapon-free-2025-07-03/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2791,21 +2593,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Safety of Nuclear Fuel Reprocessing Facilities</t>
+          <t>Iran won’t attack the US but will continue nuclear development, senior Iranian official says</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2825,43 +2627,38 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15774/safety-of-nuclear-fuel-reprocessing-facilities</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://www.politico.com/news/2025/07/03/iran-us-bombing-retaliation-00439125</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Safety of Nuclear Fuel Reprocessing Facilities</t>
+          <t>US and Iran to resume nuclear talks next week, provided Trump refrains from military action during negotiations</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2876,409 +2673,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15774/safety-of-nuclear-fuel-reprocessing-facilities</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>World’s first nuclear microreactor test bed launches at Idaho National Laboratory</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Idaho</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>45840</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://interestingengineering.com/energy/dome-microreactor-testing-westinghouse-radiant</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>(43.4887907, -112.03628)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>World’s first nuclear reactor producing 200 tons of hydrogen daily launched in US</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>45840</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>https://interestingengineering.com/energy/worlds-first-nuclear-reactor-producing-hydrogen</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>(45.3573429, -122.606758)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>USAID defunding could lead to 14 million deaths worldwide from infectious diseases by 2030</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Washington D.C.</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>https://www.cidrap.umn.edu/hivaids/usaid-defunding-could-lead-14-million-deaths-worldwide-infectious-diseases-2030</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Iran’s president orders country to suspend cooperation with IAEA</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Tehran</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>45840</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>https://gulfnews.com/world/mena/3rd-ld-writethru-250-1.500184244</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>China says it is willing to take lead in signing Southeast Asia nuclear weapon-free zone treaty</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>45841</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>https://www.reuters.com/world/china/china-says-it-is-willing-take-lead-signing-southeast-asia-nuclear-weapon-free-2025-07-03/</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>(22.2088246, 107.2173992)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Iran won’t attack the US but will continue nuclear development, senior Iranian official says</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Tehran</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>45841</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://www.politico.com/news/2025/07/03/iran-us-bombing-retaliation-00439125</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>US and Iran to resume nuclear talks next week, provided Trump refrains from military action during negotiations</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Tehran</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>45842</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
           <t>https://www.theweek.in/news/middle-east/2025/07/04/us-and-iran-to-resume-nuclear-talks-next-week-provided-trump-refrains-from-military-action-during-negotiations.html</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>(35.6892523, 51.3896004)</t>
         </is>
       </c>
     </row>
